--- a/Data/Bronze/MCIC-PROFUNDIZACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 9. BIENESTAR DE LA COMUNIDAD ACADÉMICA DEL PROGRAMA/b. Divulgación de los servicios ofrecidos por Bienestar/F9_Bienestar_Profundizacion.xlsx
+++ b/Data/Bronze/MCIC-PROFUNDIZACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 9. BIENESTAR DE LA COMUNIDAD ACADÉMICA DEL PROGRAMA/b. Divulgación de los servicios ofrecidos por Bienestar/F9_Bienestar_Profundizacion.xlsx
@@ -668,7 +668,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Firmaron inducción 2026-1</t>
+          <t>Asistieron a la inducción 2026-1</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -684,7 +684,7 @@
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="9" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Inducción 2026-1: 10 estudiantes de Profundización firmaron la planilla (cohorte 2026-1 admitida: 14)</t>
+          <t>Inducción 2026-1: 10 estudiantes de Profundización asistieron (cohorte 2026-1 admitida: 14)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
